--- a/sample_gradebook_raw.xlsx
+++ b/sample_gradebook_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/colin.madland/Documents/GitHub/edci339/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F28F80E2-C6B7-604A-A0A3-2D031CF78FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE6E8A3-FF14-C24A-ABDD-FA20E38133E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28080" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gradebook" sheetId="1" r:id="rId1"/>
@@ -890,6 +890,8 @@
     <col min="2" max="10" width="13" customWidth="1"/>
     <col min="11" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="23" width="10.83203125"/>
+    <col min="24" max="24" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
@@ -1019,7 +1021,7 @@
         <v>57</v>
       </c>
       <c r="Q2" s="1">
-        <f t="shared" ref="Q2:Q33" si="0">AVERAGE(B2:P2)</f>
+        <f>AVERAGE(B2:P2)</f>
         <v>75</v>
       </c>
       <c r="R2">
@@ -1105,7 +1107,7 @@
         <v>96</v>
       </c>
       <c r="Q3" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B3:P3)</f>
         <v>75</v>
       </c>
       <c r="R3">
@@ -1191,7 +1193,7 @@
         <v>48</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B4:P4)</f>
         <v>75</v>
       </c>
       <c r="R4">
@@ -1277,7 +1279,7 @@
         <v>95</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B5:P5)</f>
         <v>75</v>
       </c>
       <c r="R5">
@@ -1363,7 +1365,7 @@
         <v>81</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B6:P6)</f>
         <v>75</v>
       </c>
       <c r="R6">
@@ -1449,7 +1451,7 @@
         <v>99</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B7:P7)</f>
         <v>75</v>
       </c>
       <c r="R7">
@@ -1535,7 +1537,7 @@
         <v>84</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B8:P8)</f>
         <v>75</v>
       </c>
       <c r="R8">
@@ -1621,7 +1623,7 @@
         <v>74</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B9:P9)</f>
         <v>75</v>
       </c>
       <c r="R9">
@@ -1707,7 +1709,7 @@
         <v>97</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B10:P10)</f>
         <v>75</v>
       </c>
       <c r="R10">
@@ -1793,7 +1795,7 @@
         <v>92</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B11:P11)</f>
         <v>75</v>
       </c>
       <c r="R11">
@@ -1879,7 +1881,7 @@
         <v>55</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B12:P12)</f>
         <v>75</v>
       </c>
       <c r="R12">
@@ -1965,7 +1967,7 @@
         <v>68</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B13:P13)</f>
         <v>75</v>
       </c>
       <c r="R13">
@@ -2051,7 +2053,7 @@
         <v>99</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B14:P14)</f>
         <v>75</v>
       </c>
       <c r="R14">
@@ -2137,7 +2139,7 @@
         <v>78</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B15:P15)</f>
         <v>75</v>
       </c>
       <c r="R15">
@@ -2223,7 +2225,7 @@
         <v>92</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B16:P16)</f>
         <v>75</v>
       </c>
       <c r="R16">
@@ -2309,7 +2311,7 @@
         <v>77</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B17:P17)</f>
         <v>75</v>
       </c>
       <c r="R17">
@@ -2395,7 +2397,7 @@
         <v>92</v>
       </c>
       <c r="Q18" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B18:P18)</f>
         <v>75</v>
       </c>
       <c r="R18">
@@ -2481,7 +2483,7 @@
         <v>85</v>
       </c>
       <c r="Q19" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B19:P19)</f>
         <v>75</v>
       </c>
       <c r="R19">
@@ -2567,7 +2569,7 @@
         <v>94</v>
       </c>
       <c r="Q20" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B20:P20)</f>
         <v>75</v>
       </c>
       <c r="R20">
@@ -2653,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B21:P21)</f>
         <v>75</v>
       </c>
       <c r="R21">
@@ -2739,7 +2741,7 @@
         <v>91</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B22:P22)</f>
         <v>75</v>
       </c>
       <c r="R22">
@@ -2825,7 +2827,7 @@
         <v>85</v>
       </c>
       <c r="Q23" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B23:P23)</f>
         <v>75</v>
       </c>
       <c r="R23">
@@ -2911,7 +2913,7 @@
         <v>88</v>
       </c>
       <c r="Q24" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B24:P24)</f>
         <v>75</v>
       </c>
       <c r="R24">
@@ -2997,7 +2999,7 @@
         <v>58</v>
       </c>
       <c r="Q25" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B25:P25)</f>
         <v>75</v>
       </c>
       <c r="R25">
@@ -3083,7 +3085,7 @@
         <v>90</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B26:P26)</f>
         <v>75</v>
       </c>
       <c r="R26">
@@ -3169,7 +3171,7 @@
         <v>19</v>
       </c>
       <c r="Q27" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B27:P27)</f>
         <v>75</v>
       </c>
       <c r="R27">
@@ -3255,7 +3257,7 @@
         <v>94</v>
       </c>
       <c r="Q28" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B28:P28)</f>
         <v>75</v>
       </c>
       <c r="R28">
@@ -3341,7 +3343,7 @@
         <v>47</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B29:P29)</f>
         <v>75</v>
       </c>
       <c r="R29">
@@ -3427,7 +3429,7 @@
         <v>96</v>
       </c>
       <c r="Q30" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B30:P30)</f>
         <v>75</v>
       </c>
       <c r="R30">
@@ -3513,7 +3515,7 @@
         <v>58</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B31:P31)</f>
         <v>75</v>
       </c>
       <c r="R31">
@@ -3599,7 +3601,7 @@
         <v>92</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B32:P32)</f>
         <v>75</v>
       </c>
       <c r="R32">
@@ -3685,7 +3687,7 @@
         <v>66</v>
       </c>
       <c r="Q33" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(B33:P33)</f>
         <v>75</v>
       </c>
       <c r="R33">
@@ -3771,7 +3773,7 @@
         <v>93</v>
       </c>
       <c r="Q34" s="1">
-        <f t="shared" ref="Q34:Q65" si="1">AVERAGE(B34:P34)</f>
+        <f>AVERAGE(B34:P34)</f>
         <v>75</v>
       </c>
       <c r="R34">
@@ -3857,7 +3859,7 @@
         <v>70</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B35:P35)</f>
         <v>75</v>
       </c>
       <c r="R35">
@@ -3943,7 +3945,7 @@
         <v>74</v>
       </c>
       <c r="Q36" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B36:P36)</f>
         <v>75</v>
       </c>
       <c r="R36">
@@ -4029,7 +4031,7 @@
         <v>99</v>
       </c>
       <c r="Q37" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B37:P37)</f>
         <v>75</v>
       </c>
       <c r="R37">
@@ -4115,7 +4117,7 @@
         <v>56</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B38:P38)</f>
         <v>75</v>
       </c>
       <c r="R38">
@@ -4201,7 +4203,7 @@
         <v>94</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B39:P39)</f>
         <v>75</v>
       </c>
       <c r="R39">
@@ -4287,7 +4289,7 @@
         <v>85</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B40:P40)</f>
         <v>75</v>
       </c>
       <c r="R40">
@@ -4373,7 +4375,7 @@
         <v>87</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B41:P41)</f>
         <v>75</v>
       </c>
       <c r="R41">
@@ -4459,7 +4461,7 @@
         <v>92</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B42:P42)</f>
         <v>75</v>
       </c>
       <c r="R42">
@@ -4545,7 +4547,7 @@
         <v>26</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B43:P43)</f>
         <v>75</v>
       </c>
       <c r="R43">
@@ -4631,7 +4633,7 @@
         <v>88</v>
       </c>
       <c r="Q44" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B44:P44)</f>
         <v>75</v>
       </c>
       <c r="R44">
@@ -4717,7 +4719,7 @@
         <v>45</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B45:P45)</f>
         <v>75</v>
       </c>
       <c r="R45">
@@ -4803,7 +4805,7 @@
         <v>38</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B46:P46)</f>
         <v>75</v>
       </c>
       <c r="R46">
@@ -4889,7 +4891,7 @@
         <v>95</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B47:P47)</f>
         <v>75</v>
       </c>
       <c r="R47">
@@ -4975,7 +4977,7 @@
         <v>46</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B48:P48)</f>
         <v>75</v>
       </c>
       <c r="R48">
@@ -5061,7 +5063,7 @@
         <v>90</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B49:P49)</f>
         <v>75</v>
       </c>
       <c r="R49">
@@ -5147,7 +5149,7 @@
         <v>63</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B50:P50)</f>
         <v>75</v>
       </c>
       <c r="R50">
@@ -5233,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B51:P51)</f>
         <v>75</v>
       </c>
       <c r="R51">
@@ -5319,7 +5321,7 @@
         <v>90</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B52:P52)</f>
         <v>75</v>
       </c>
       <c r="R52">
@@ -5405,7 +5407,7 @@
         <v>91</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B53:P53)</f>
         <v>75</v>
       </c>
       <c r="R53">
@@ -5491,7 +5493,7 @@
         <v>81</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B54:P54)</f>
         <v>75</v>
       </c>
       <c r="R54">
@@ -5577,7 +5579,7 @@
         <v>76</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B55:P55)</f>
         <v>75</v>
       </c>
       <c r="R55">
@@ -5663,7 +5665,7 @@
         <v>73</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B56:P56)</f>
         <v>75</v>
       </c>
       <c r="R56">
@@ -5749,7 +5751,7 @@
         <v>76</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B57:P57)</f>
         <v>75</v>
       </c>
       <c r="R57">
@@ -5835,7 +5837,7 @@
         <v>84</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B58:P58)</f>
         <v>75</v>
       </c>
       <c r="R58">
@@ -5921,7 +5923,7 @@
         <v>81</v>
       </c>
       <c r="Q59" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B59:P59)</f>
         <v>75</v>
       </c>
       <c r="R59">
@@ -6007,7 +6009,7 @@
         <v>77</v>
       </c>
       <c r="Q60" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B60:P60)</f>
         <v>75</v>
       </c>
       <c r="R60">
@@ -6093,7 +6095,7 @@
         <v>68</v>
       </c>
       <c r="Q61" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B61:P61)</f>
         <v>75</v>
       </c>
       <c r="R61">
@@ -6179,7 +6181,7 @@
         <v>96</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B62:P62)</f>
         <v>75</v>
       </c>
       <c r="R62">
@@ -6265,7 +6267,7 @@
         <v>42</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B63:P63)</f>
         <v>75</v>
       </c>
       <c r="R63">
@@ -6351,7 +6353,7 @@
         <v>98</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B64:P64)</f>
         <v>75</v>
       </c>
       <c r="R64">
@@ -6437,7 +6439,7 @@
         <v>99</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="1"/>
+        <f>AVERAGE(B65:P65)</f>
         <v>75</v>
       </c>
       <c r="R65">
@@ -6523,7 +6525,7 @@
         <v>99</v>
       </c>
       <c r="Q66" s="1">
-        <f t="shared" ref="Q66:Q97" si="2">AVERAGE(B66:P66)</f>
+        <f>AVERAGE(B66:P66)</f>
         <v>75</v>
       </c>
       <c r="R66">
@@ -6609,7 +6611,7 @@
         <v>98</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B67:P67)</f>
         <v>75</v>
       </c>
       <c r="R67">
@@ -6695,7 +6697,7 @@
         <v>88</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B68:P68)</f>
         <v>75</v>
       </c>
       <c r="R68">
@@ -6781,7 +6783,7 @@
         <v>71</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B69:P69)</f>
         <v>75</v>
       </c>
       <c r="R69">
@@ -6867,7 +6869,7 @@
         <v>99</v>
       </c>
       <c r="Q70" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B70:P70)</f>
         <v>75</v>
       </c>
       <c r="R70">
@@ -6953,7 +6955,7 @@
         <v>93</v>
       </c>
       <c r="Q71" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B71:P71)</f>
         <v>75</v>
       </c>
       <c r="R71">
@@ -7039,7 +7041,7 @@
         <v>98</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B72:P72)</f>
         <v>75</v>
       </c>
       <c r="R72">
@@ -7125,7 +7127,7 @@
         <v>64</v>
       </c>
       <c r="Q73" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B73:P73)</f>
         <v>75</v>
       </c>
       <c r="R73">
@@ -7211,7 +7213,7 @@
         <v>76</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B74:P74)</f>
         <v>75</v>
       </c>
       <c r="R74">
@@ -7297,7 +7299,7 @@
         <v>84</v>
       </c>
       <c r="Q75" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B75:P75)</f>
         <v>75</v>
       </c>
       <c r="R75">
@@ -7383,7 +7385,7 @@
         <v>60</v>
       </c>
       <c r="Q76" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B76:P76)</f>
         <v>75</v>
       </c>
       <c r="R76">
@@ -7469,7 +7471,7 @@
         <v>76</v>
       </c>
       <c r="Q77" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B77:P77)</f>
         <v>75</v>
       </c>
       <c r="R77">
@@ -7555,7 +7557,7 @@
         <v>91</v>
       </c>
       <c r="Q78" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B78:P78)</f>
         <v>75</v>
       </c>
       <c r="R78">
@@ -7641,7 +7643,7 @@
         <v>98</v>
       </c>
       <c r="Q79" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B79:P79)</f>
         <v>75</v>
       </c>
       <c r="R79">
@@ -7727,7 +7729,7 @@
         <v>98</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B80:P80)</f>
         <v>75</v>
       </c>
       <c r="R80">
@@ -7813,7 +7815,7 @@
         <v>94</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B81:P81)</f>
         <v>75</v>
       </c>
       <c r="R81">
@@ -7899,7 +7901,7 @@
         <v>73</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B82:P82)</f>
         <v>75</v>
       </c>
       <c r="R82">
@@ -7985,7 +7987,7 @@
         <v>80</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B83:P83)</f>
         <v>75</v>
       </c>
       <c r="R83">
@@ -8071,7 +8073,7 @@
         <v>79</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B84:P84)</f>
         <v>75</v>
       </c>
       <c r="R84">
@@ -8157,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B85:P85)</f>
         <v>75</v>
       </c>
       <c r="R85">
@@ -8243,7 +8245,7 @@
         <v>91</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B86:P86)</f>
         <v>75</v>
       </c>
       <c r="R86">
@@ -8329,7 +8331,7 @@
         <v>68</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B87:P87)</f>
         <v>75</v>
       </c>
       <c r="R87">
@@ -8415,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B88:P88)</f>
         <v>75</v>
       </c>
       <c r="R88">
@@ -8501,7 +8503,7 @@
         <v>73</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B89:P89)</f>
         <v>75</v>
       </c>
       <c r="R89">
@@ -8587,7 +8589,7 @@
         <v>61</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B90:P90)</f>
         <v>75</v>
       </c>
       <c r="R90">
@@ -8673,7 +8675,7 @@
         <v>95</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B91:P91)</f>
         <v>75</v>
       </c>
       <c r="R91">
@@ -8759,7 +8761,7 @@
         <v>37</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B92:P92)</f>
         <v>75</v>
       </c>
       <c r="R92">
@@ -8845,7 +8847,7 @@
         <v>82</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B93:P93)</f>
         <v>75</v>
       </c>
       <c r="R93">
@@ -8931,7 +8933,7 @@
         <v>74</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B94:P94)</f>
         <v>75</v>
       </c>
       <c r="R94">
@@ -9017,7 +9019,7 @@
         <v>84</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B95:P95)</f>
         <v>75</v>
       </c>
       <c r="R95">
@@ -9103,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B96:P96)</f>
         <v>75</v>
       </c>
       <c r="R96">
@@ -9189,7 +9191,7 @@
         <v>63</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B97:P97)</f>
         <v>75</v>
       </c>
       <c r="R97">
@@ -9275,7 +9277,7 @@
         <v>74</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" ref="Q98:Q101" si="3">AVERAGE(B98:P98)</f>
+        <f>AVERAGE(B98:P98)</f>
         <v>75</v>
       </c>
       <c r="R98">
@@ -9361,7 +9363,7 @@
         <v>64</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(B99:P99)</f>
         <v>75</v>
       </c>
       <c r="R99">
@@ -9447,7 +9449,7 @@
         <v>44</v>
       </c>
       <c r="Q100" s="1">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(B100:P100)</f>
         <v>75</v>
       </c>
       <c r="R100">
@@ -9533,7 +9535,7 @@
         <v>90</v>
       </c>
       <c r="Q101" s="1">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(B101:P101)</f>
         <v>75</v>
       </c>
       <c r="R101">
